--- a/datasets/agenda_implementation/data/output/procedure_references.xlsx
+++ b/datasets/agenda_implementation/data/output/procedure_references.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI0087</t>
+          <t>AI0090</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI0088</t>
+          <t>AI0091</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AI0089</t>
+          <t>AI0092</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI0090</t>
+          <t>AI0093</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AI0091</t>
+          <t>AI0094</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AI0092</t>
+          <t>AI0095</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AI0093</t>
+          <t>AI0096</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AI0094</t>
+          <t>AI0097</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AI0095</t>
+          <t>AI0098</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AI0096</t>
+          <t>AI0099</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AI0097</t>
+          <t>AI0100</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AI0098</t>
+          <t>AI0101</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AI0099</t>
+          <t>AI0102</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AI0100</t>
+          <t>AI0103</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AI0101</t>
+          <t>AI0104</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AI0102</t>
+          <t>AI0105</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AI0103</t>
+          <t>AI0106</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AI0104</t>
+          <t>AI0107</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AI0105</t>
+          <t>AI0108</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AI0106</t>
+          <t>AI0109</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AI0107</t>
+          <t>AI0110</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AI0108</t>
+          <t>AI0111</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AI0109</t>
+          <t>AI0112</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AI0110</t>
+          <t>AI0113</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AI0111</t>
+          <t>AI0114</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AI0112</t>
+          <t>AI0115</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AI0113</t>
+          <t>AI0116</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AI0113</t>
+          <t>AI0116</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AI0114</t>
+          <t>AI0117</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AI0115</t>
+          <t>AI0118</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AI0116</t>
+          <t>AI0119</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AI0117</t>
+          <t>AI0120</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AI0118</t>
+          <t>AI0121</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AI0119</t>
+          <t>AI0122</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AI0120</t>
+          <t>AI0123</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AI0121</t>
+          <t>AI0124</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AI0122</t>
+          <t>AI0125</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AI0123</t>
+          <t>AI0126</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
